--- a/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
@@ -1153,25 +1153,25 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1252,25 +1252,25 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1287,25 +1287,25 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>3.4</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1322,25 +1322,25 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>6.1</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1354,25 +1354,25 @@
         <v>62</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F8">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1389,25 +1389,25 @@
         <v>12</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1421,25 +1421,25 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1456,25 +1456,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1526,25 +1526,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>8.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="J15">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1631,25 +1631,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1663,25 +1663,25 @@
         <v>197</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="F17">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>18.3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1692,25 +1692,25 @@
         <v>319</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="F18">
-        <v>319</v>
+        <v>41</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>319</v>
+        <v>24</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
@@ -1561,25 +1561,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1663,25 +1663,25 @@
         <v>197</v>
       </c>
       <c r="E17">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="F17">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>81.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>18.3</v>
+        <v>6.6</v>
       </c>
       <c r="I17" s="2">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1692,25 +1692,25 @@
         <v>319</v>
       </c>
       <c r="E18">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="F18">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="G18" s="1">
-        <v>87.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>12.9</v>
+        <v>5.6</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
@@ -1778,25 +1778,25 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1810,25 +1810,25 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1845,25 +1845,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1877,25 +1877,25 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1912,25 +1912,25 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1947,25 +1947,25 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>12.1</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1979,25 +1979,25 @@
         <v>62</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F8">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J8">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2014,25 +2014,25 @@
         <v>12</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2046,25 +2046,25 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2081,25 +2081,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2116,25 +2116,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2151,25 +2151,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>8.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2186,25 +2186,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2221,25 +2221,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="J15">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2256,25 +2256,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2288,25 +2288,25 @@
         <v>197</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="F17">
-        <v>197</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J17">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2317,25 +2317,25 @@
         <v>319</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="F18">
-        <v>319</v>
+        <v>36</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>88.7</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>11.3</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J18">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20232.xlsx
@@ -1912,19 +1912,19 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>69</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>31</v>
+        <v>6.9</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1947,19 +1947,19 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1979,19 +1979,19 @@
         <v>62</v>
       </c>
       <c r="E8">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>79</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>21</v>
+        <v>8.1</v>
       </c>
       <c r="I8" s="2">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2014,19 +2014,19 @@
         <v>12</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="H9" s="1">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2046,19 +2046,19 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="H10" s="1">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2317,19 +2317,19 @@
         <v>319</v>
       </c>
       <c r="E18">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="F18">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1">
-        <v>88.7</v>
+        <v>91.5</v>
       </c>
       <c r="H18" s="1">
-        <v>11.3</v>
+        <v>8.5</v>
       </c>
       <c r="I18" s="2">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J18">
         <v>0</v>
